--- a/reference/kahoot/out/kahoot-9/kahoot-9.xlsx
+++ b/reference/kahoot/out/kahoot-9/kahoot-9.xlsx
@@ -467,34 +467,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Блок схемд "12 ба түүнээс дээш настай юу?" гэсэн асуултыг ямар дүрсээр зурах вэ?</t>
+          <t>Бат яг 16 настай. Энэ схемээр юу гарах вэ?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Тэгш өнцөгт</t>
+          <t>Гоймон авч болохгүй</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Налуу</t>
+          <t>Гоймон авч болно</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ромбо</t>
+          <t>Хоёулаа гарна</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Зууван</t>
+          <t>Юу ч гарахгүй</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -503,34 +503,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>x = 8 үед хоёр мөрөнд юу гарах вэ?</t>
+          <t>Лифтэнд яг 500 кг хүн орвол юу болох вэ?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>true, true</t>
+          <t>Хэт ачаалал!</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>true, false</t>
+          <t>Хоёулаа гарна</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>false, true</t>
+          <t>Хаалга хаагдана</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>false, false</t>
+          <t>Юу ч гарахгүй</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -539,34 +539,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Энэ блок схемийг дагавал юу гарах вэ?</t>
+          <t>Сараа зөв PIN 1234-өө дарлаа. Утас нээгдэх үү?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Болохгүй</t>
+          <t>Нээгдэнэ — Түгжээ нээгдлээ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Болохгүй, Болно</t>
+          <t>Нээгдэхгүй — PIN буруу</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Юу ч гарахгүй</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Болно</t>
+          <t>Хоёулаа гарна</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -575,34 +575,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Хашилттай "5"-ийг 5 тоотой === -ээр жишвэл?</t>
+          <t>Тоглоомд 40 оноо авсан. Console-д юу гарах вэ?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>Шинэ рекорд!, 40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Алдаа гарна</t>
+          <t>Шинэ рекорд!, 100</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -611,34 +611,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>x = 4 байхад if дотор нэг = бичвэл юу болох вэ?</t>
+          <t>Тэргүүн байр эзэлсэн хүүхэд юу авах вэ?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Юу ч гарахгүй</t>
+          <t>Алтан аяга</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Алдаа гарна</t>
+          <t>Медаль</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10 байна</t>
+          <t>Медаль, Алтан аяга</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Баярлалаа</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>60</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -647,34 +647,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>35 градуст юу гарах вэ?</t>
+          <t>Цаг 21 болж байна. Ээж юу гэх вэ?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Шорт</t>
+          <t>Шүдээ угаа</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Өмд цамц</t>
+          <t>Унт!, Шүдээ угаа</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Өмд цамц, Шорт</t>
+          <t>Юу ч хэлэхгүй</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Гадуур хувцас</t>
+          <t>Алдаа: else дутуу</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>60</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -683,34 +683,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>else бичээгүй. Console-д юу гарах вэ?</t>
+          <t>15 настай Тэмүүлэн 12000₮-тэй. Кинонд орох уу?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Дууслаа</t>
+          <t>Орно — нас нь хүрч байна</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Их, Дууслаа</t>
+          <t>Хоёулаа гарна</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Юу ч гарахгүй</t>
+          <t>Гэртээ үлдэнэ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Алдаа: else дутуу</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>60</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -719,22 +719,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13 настай, тасалбаргүй. Юу гарах вэ?</t>
+          <t>Өнөөдөр "Ням" (том Н). Амрах уу?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Орж болно</t>
+          <t>Амралт!</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Орж болно, Орж болохгүй</t>
+          <t>Хичээлдээ яв</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Орж болохгүй</t>
+          <t>Хоёулаа гарна</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -746,7 +746,7 @@
         <v>60</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -755,34 +755,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Тэгш тоонд "тэгш" гаргахын тулд шар ромбод юу бичих вэ?</t>
+          <t>Өнөөдөр зөвхөн тэгш дугаартай машин явна. Шар хэсэгт юу бичих вэ?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>x / 2 === 0 ?</t>
+          <t>dugaar / 2 === 0 ?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>x % 2 = 0 ?</t>
+          <t>dugaar % 2 = 0 ?</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>x % 2 === 2 ?</t>
+          <t>dugaar % 2 === 0 ?</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>x % 2 === 0 ?</t>
+          <t>dugaar % 2 === 1 ?</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>60</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -791,34 +791,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>odor = "Ням" (том Н) үед юу гарах вэ?</t>
+          <t>110 см өндөр дүү аттракционд сууж чадах уу?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Амралт</t>
+          <t>Юу ч гарахгүй</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Хичээл</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Амралт, Хичээл</t>
+          <t>Сууж болно</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Алдаа гарна</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>60</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -827,27 +827,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Яг 80 оноо авбал ямар дүн гарах вэ?</t>
+          <t>Зөв ажиллахын тулд ??? -ийн оронд аль нь вэ?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>nuuts === oruulsan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>nuuts !== oruulsan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>nuuts = oruulsan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A, B</t>
+          <t>nuuts !== "oruulsan"</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -863,27 +863,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>else-ийн араас else if бичвэл юу болох вэ?</t>
+          <t>Бямба гараг, бороо орж байна. Юу хийх вэ?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Бага</t>
+          <t>Парк руу!</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Дунд</t>
+          <t>Хоёулаа</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Бага, Дунд</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Алдаа гарна</t>
+          <t>Гэртээ кино</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -899,34 +899,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>n = 15 үед энэ код юу гаргах вэ?</t>
+          <t>20 градуст юу өмсөх вэ?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FizzBuzz</t>
+          <t>Цамц</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fizz</t>
+          <t>Куртка</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fizz, Buzz</t>
+          <t>Алдаа гарна</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>Куртка, Цамц</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>60</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -935,27 +935,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Зөв ажиллахын тулд ??? -ийн оронд аль нь вэ?</t>
+          <t>Аль хурдтай машин 20000₮ торгууль төлөх вэ?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>x % 2 === 0</t>
+          <t>80 км/ц</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>x % 2 !== 0</t>
+          <t>100 км/ц</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>x % 2 = 1</t>
+          <t>101 км/ц</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>x / 2 !== 0</t>
+          <t>120 км/ц</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -971,27 +971,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Аль насанд "Хөнгөлөлттэй" гарах вэ?</t>
+          <t>Хэн автобусанд үнэгүй суух вэ?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nas = 6</t>
+          <t>6 настай дүү</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>nas = 59</t>
+          <t>59 настай аав</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>nas = 60</t>
+          <t>60 настай эмээ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nas = 30</t>
+          <t>30 настай ах</t>
         </is>
       </c>
       <c r="G23" t="n">
